--- a/assets/models/機台尺寸.xlsx
+++ b/assets/models/機台尺寸.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\.gemini\antigravity\playground\webxr-survey-app\assets\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC5039FB-BAA1-4033-BEBD-14DEC11C1222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3523C81-71A7-4D27-8CDE-41137BA147BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11450" yWindow="2290" windowWidth="17170" windowHeight="14350" xr2:uid="{52D6DD54-03CB-4AC6-8763-E74045D7A1BD}"/>
   </bookViews>
@@ -562,58 +562,58 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1643,53 +1643,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="210" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="5"/>
-      <c r="B1" s="6"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="6"/>
+      <c r="A1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="21"/>
       <c r="G1" s="2" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15" t="e" vm="2">
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15"/>
-      <c r="X1" s="15" t="e" vm="3">
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="15"/>
-      <c r="AA1" s="15"/>
-      <c r="AB1" s="15"/>
-      <c r="AC1" s="15"/>
-      <c r="AD1" s="15" t="e" vm="4">
+      <c r="Y1" s="6"/>
+      <c r="Z1" s="6"/>
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6"/>
+      <c r="AD1" s="6" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="AE1" s="15"/>
-      <c r="AF1" s="15"/>
-      <c r="AG1" s="15"/>
+      <c r="AE1" s="6"/>
+      <c r="AF1" s="6"/>
+      <c r="AG1" s="6"/>
     </row>
     <row r="2" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="12"/>
+      <c r="B2" s="13"/>
       <c r="C2" s="7" t="s">
         <v>21</v>
       </c>
@@ -1698,17 +1698,17 @@
         <v>22</v>
       </c>
       <c r="F2" s="8"/>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="8"/>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="12"/>
+      <c r="K2" s="13"/>
       <c r="L2" s="7" t="s">
         <v>12</v>
       </c>
@@ -1717,18 +1717,18 @@
         <v>13</v>
       </c>
       <c r="O2" s="8"/>
-      <c r="P2" s="11" t="s">
+      <c r="P2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="12"/>
+      <c r="Q2" s="13"/>
       <c r="R2" s="7" t="s">
         <v>35</v>
       </c>
       <c r="S2" s="8"/>
-      <c r="T2" s="11" t="s">
+      <c r="T2" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="U2" s="12"/>
+      <c r="U2" s="13"/>
       <c r="V2" s="7" t="s">
         <v>37</v>
       </c>
@@ -1737,10 +1737,10 @@
         <v>38</v>
       </c>
       <c r="Y2" s="8"/>
-      <c r="Z2" s="11" t="s">
+      <c r="Z2" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="AA2" s="12"/>
+      <c r="AA2" s="13"/>
       <c r="AB2" s="7" t="s">
         <v>43</v>
       </c>
@@ -1749,16 +1749,16 @@
         <v>17</v>
       </c>
       <c r="AE2" s="8"/>
-      <c r="AF2" s="11" t="s">
+      <c r="AF2" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="AG2" s="12"/>
+      <c r="AG2" s="13"/>
     </row>
     <row r="3" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="14"/>
+      <c r="B3" s="15"/>
       <c r="C3" s="9" t="s">
         <v>27</v>
       </c>
@@ -1767,17 +1767,17 @@
         <v>27</v>
       </c>
       <c r="F3" s="10"/>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="5" t="s">
         <v>26</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>24</v>
       </c>
       <c r="I3" s="10"/>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="14"/>
+      <c r="K3" s="15"/>
       <c r="L3" s="9" t="s">
         <v>30</v>
       </c>
@@ -1786,18 +1786,18 @@
         <v>2</v>
       </c>
       <c r="O3" s="10"/>
-      <c r="P3" s="13" t="s">
+      <c r="P3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="Q3" s="14"/>
+      <c r="Q3" s="15"/>
       <c r="R3" s="9" t="s">
         <v>24</v>
       </c>
       <c r="S3" s="10"/>
-      <c r="T3" s="13" t="s">
+      <c r="T3" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="U3" s="14"/>
+      <c r="U3" s="15"/>
       <c r="V3" s="9" t="s">
         <v>30</v>
       </c>
@@ -1806,116 +1806,127 @@
         <v>2</v>
       </c>
       <c r="Y3" s="10"/>
-      <c r="Z3" s="13" t="s">
+      <c r="Z3" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="AA3" s="14"/>
+      <c r="AA3" s="15"/>
       <c r="AB3" s="9" t="s">
         <v>24</v>
       </c>
       <c r="AC3" s="10"/>
-      <c r="AD3" s="20" t="s">
+      <c r="AD3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="AE3" s="21"/>
+      <c r="AE3" s="17"/>
       <c r="AF3" s="18" t="s">
         <v>1</v>
       </c>
       <c r="AG3" s="19"/>
     </row>
     <row r="4" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="11"/>
+      <c r="C4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4" t="s">
+      <c r="D4" s="11"/>
+      <c r="E4" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="4"/>
+      <c r="F4" s="11"/>
       <c r="G4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4" t="s">
+      <c r="I4" s="11"/>
+      <c r="J4" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4" t="s">
+      <c r="K4" s="11"/>
+      <c r="L4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4" t="s">
+      <c r="M4" s="11"/>
+      <c r="N4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4" t="s">
+      <c r="O4" s="11"/>
+      <c r="P4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4" t="s">
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4" t="s">
+      <c r="S4" s="11"/>
+      <c r="T4" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4" t="s">
+      <c r="U4" s="11"/>
+      <c r="V4" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4" t="s">
+      <c r="W4" s="11"/>
+      <c r="X4" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="4" t="s">
+      <c r="Y4" s="11"/>
+      <c r="Z4" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="AA4" s="4"/>
-      <c r="AB4" s="4" t="s">
+      <c r="AA4" s="11"/>
+      <c r="AB4" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="AC4" s="4"/>
-      <c r="AD4" s="4" t="s">
+      <c r="AC4" s="11"/>
+      <c r="AD4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="AE4" s="4"/>
-      <c r="AF4" s="4" t="s">
+      <c r="AE4" s="11"/>
+      <c r="AF4" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="AG4" s="4"/>
+      <c r="AG4" s="11"/>
     </row>
     <row r="8" spans="1:33" ht="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:33" ht="9.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="22" ht="9" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AB2:AC2"/>
-    <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="AD4:AE4"/>
+    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AD2:AE2"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AF2:AG2"/>
+    <mergeCell ref="AF3:AG3"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="P3:Q3"/>
@@ -1929,38 +1940,27 @@
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="N1:O1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AD2:AE2"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AF2:AG2"/>
-    <mergeCell ref="AF3:AG3"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="N3:O3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="AD4:AE4"/>
-    <mergeCell ref="AF4:AG4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AB2:AC2"/>
+    <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="Z3:AA3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
